--- a/output/table_12_bop.xlsx
+++ b/output/table_12_bop.xlsx
@@ -823,31 +823,31 @@
         </is>
       </c>
       <c r="B12">
-        <v>60.8</v>
+        <v>58.6</v>
       </c>
       <c r="C12">
-        <v>161.1</v>
+        <v>159</v>
       </c>
       <c r="D12">
-        <v>40.4</v>
+        <v>38.3</v>
       </c>
       <c r="E12">
-        <v>150.5</v>
+        <v>148.7</v>
       </c>
       <c r="F12">
-        <v>351</v>
+        <v>349.1</v>
       </c>
       <c r="G12">
-        <v>570.2</v>
+        <v>568.5</v>
       </c>
       <c r="H12">
-        <v>742.3</v>
+        <v>740.3</v>
       </c>
       <c r="I12">
-        <v>541.5</v>
+        <v>539.1</v>
       </c>
       <c r="J12">
-        <v>729.1</v>
+        <v>726.2</v>
       </c>
       <c r="K12">
         <v>843.5</v>
@@ -903,31 +903,31 @@
         </is>
       </c>
       <c r="B14">
-        <v>169.3</v>
+        <v>167.1</v>
       </c>
       <c r="C14">
-        <v>125.6</v>
+        <v>123.5</v>
       </c>
       <c r="D14">
-        <v>-121.9</v>
+        <v>-124.1</v>
       </c>
       <c r="E14">
-        <v>111.6</v>
+        <v>109.8</v>
       </c>
       <c r="F14">
-        <v>441.3</v>
+        <v>439.4</v>
       </c>
       <c r="G14">
-        <v>401.2</v>
+        <v>399.5</v>
       </c>
       <c r="H14">
-        <v>278</v>
+        <v>275.9</v>
       </c>
       <c r="I14">
-        <v>288.7</v>
+        <v>286.3</v>
       </c>
       <c r="J14">
-        <v>530.6</v>
+        <v>527.7</v>
       </c>
       <c r="K14">
         <v>735.6</v>
@@ -1183,31 +1183,31 @@
         </is>
       </c>
       <c r="B21">
-        <v>-73.59999999999999</v>
+        <v>-75.7</v>
       </c>
       <c r="C21">
-        <v>5.1</v>
+        <v>3</v>
       </c>
       <c r="D21">
-        <v>146</v>
+        <v>143.8</v>
       </c>
       <c r="E21">
-        <v>120.8</v>
+        <v>119</v>
       </c>
       <c r="F21">
-        <v>-52.9</v>
+        <v>-54.8</v>
       </c>
       <c r="G21">
-        <v>161</v>
+        <v>159.3</v>
       </c>
       <c r="H21">
-        <v>352.2</v>
+        <v>350.1</v>
       </c>
       <c r="I21">
-        <v>181.6</v>
+        <v>179.3</v>
       </c>
       <c r="J21">
-        <v>156.6</v>
+        <v>153.7</v>
       </c>
       <c r="K21">
         <v>105.9</v>
@@ -1263,31 +1263,31 @@
         </is>
       </c>
       <c r="B23">
-        <v>-28.3</v>
+        <v>-30.5</v>
       </c>
       <c r="C23">
-        <v>-40.8</v>
+        <v>-42.9</v>
       </c>
       <c r="D23">
-        <v>-22</v>
+        <v>-24.1</v>
       </c>
       <c r="E23">
-        <v>13.5</v>
+        <v>11.7</v>
       </c>
       <c r="F23">
-        <v>-24.3</v>
+        <v>-26.2</v>
       </c>
       <c r="G23">
-        <v>-1.7</v>
+        <v>-3.5</v>
       </c>
       <c r="H23">
-        <v>-47.2</v>
+        <v>-49.2</v>
       </c>
       <c r="I23">
-        <v>-35.5</v>
+        <v>-37.8</v>
       </c>
       <c r="J23">
-        <v>-7.1</v>
+        <v>-10</v>
       </c>
       <c r="K23">
         <v>-10.3</v>
@@ -1423,31 +1423,31 @@
         </is>
       </c>
       <c r="B27">
-        <v>273.8</v>
+        <v>271.7</v>
       </c>
       <c r="C27">
-        <v>459</v>
+        <v>456.9</v>
       </c>
       <c r="D27">
-        <v>360.3</v>
+        <v>358.1</v>
       </c>
       <c r="E27">
-        <v>379.6</v>
+        <v>377.8</v>
       </c>
       <c r="F27">
-        <v>293.5</v>
+        <v>291.6</v>
       </c>
       <c r="G27">
-        <v>830</v>
+        <v>828.2</v>
       </c>
       <c r="H27">
-        <v>430.5</v>
+        <v>428.5</v>
       </c>
       <c r="I27">
-        <v>274.8</v>
+        <v>272.5</v>
       </c>
       <c r="J27">
-        <v>479.5</v>
+        <v>476.6</v>
       </c>
       <c r="K27">
         <v>415.3</v>
